--- a/TestData/base.xlsx
+++ b/TestData/base.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,40 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>v7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>k12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>v12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>v12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>k13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>v13</t>
         </is>
       </c>
     </row>
